--- a/artfynd/A 29514-2024 artfynd.xlsx
+++ b/artfynd/A 29514-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59921461</v>
+        <v>16762750</v>
       </c>
       <c r="B2" t="n">
-        <v>108386</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231366</v>
+        <v>224363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspelandsfibbla</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium paralium</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Dahlst. ex Johanss. &amp; Sam.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kobbosjön, 830 m O sjöns ostspets, Ög</t>
+          <t>Kobbosjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554824</v>
+        <v>555100</v>
       </c>
       <c r="R2" t="n">
-        <v>6411104</v>
+        <v>6411073</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2013-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2013-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,40 +755,145 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>Skogsbilväg, bäck</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Lars Nilsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lars Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>59921461</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109702</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>231366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aspelandsfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hieracium paralium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Dahlst. ex Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kobbosjön, 830 m O sjöns ostspets, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554824</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6411104</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-06-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>grustäkt</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>AS16222</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Anders Svenson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Anders Svenson, Lars Nilsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29514-2024 artfynd.xlsx
+++ b/artfynd/A 29514-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16762750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59921461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>